--- a/AAII_Financials/Yearly/GRAB_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/GRAB_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="92">
   <si>
     <t>GRAB</t>
   </si>
@@ -656,47 +656,47 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="11" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="6" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="I7" s="2" t="s">
         <v>3</v>
       </c>
@@ -706,24 +706,27 @@
       <c r="K7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="L7" s="2"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M7" s="2"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>2359000</v>
+      </c>
+      <c r="E8" s="3">
         <v>1433000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>675000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>469000</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H8" s="3" t="s">
         <v>3</v>
       </c>
@@ -736,27 +739,30 @@
       <c r="K8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L8" s="3"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M8" s="3"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>1499000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1356000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1063000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>948000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1320000</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I9" s="3" t="s">
         <v>3</v>
       </c>
@@ -766,24 +772,27 @@
       <c r="K9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L9" s="3"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M9" s="3"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>860000</v>
+      </c>
+      <c r="E10" s="3">
         <v>77000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-388000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-479000</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H10" s="3" t="s">
         <v>3</v>
       </c>
@@ -796,9 +805,12 @@
       <c r="K10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L10" s="3"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M10" s="3"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -811,26 +823,27 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>421000</v>
+      </c>
+      <c r="E12" s="3">
         <v>466000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>356000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>257000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>231000</v>
       </c>
-      <c r="H12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I12" s="3" t="s">
         <v>3</v>
       </c>
@@ -840,9 +853,12 @@
       <c r="K12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L12" s="3"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M12" s="3"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -870,27 +886,30 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-      <c r="L13" s="3"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>128000</v>
+      </c>
+      <c r="E14" s="3">
         <v>54000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>379000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>88000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>56000</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
       </c>
@@ -900,9 +919,12 @@
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -930,9 +952,12 @@
       <c r="K15" s="3">
         <v>0</v>
       </c>
-      <c r="L15" s="3"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L15" s="3">
+        <v>0</v>
+      </c>
+      <c r="M15" s="3"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -942,26 +967,27 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2878000</v>
+      </c>
+      <c r="E17" s="3">
         <v>2806000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2583000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1782000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2165000</v>
       </c>
-      <c r="H17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I17" s="3" t="s">
         <v>3</v>
       </c>
@@ -971,24 +997,27 @@
       <c r="K17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L17" s="3"/>
-    </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M17" s="3"/>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-519000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-1373000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-1908000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-1313000</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1001,9 +1030,12 @@
       <c r="K18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L18" s="3"/>
-    </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M18" s="3"/>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1016,23 +1048,24 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>53000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-196000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>57000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1430000</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1045,27 +1078,30 @@
       <c r="K20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L20" s="3"/>
-    </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M20" s="3"/>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-321000</v>
+      </c>
+      <c r="E21" s="3">
         <v>-1419000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-1506000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-2356000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-3334000</v>
       </c>
-      <c r="H21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1075,21 +1111,24 @@
       <c r="K21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L21" s="3"/>
-    </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M21" s="3"/>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3">
         <v>165000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>1701000</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1105,27 +1144,30 @@
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L22" s="3"/>
-    </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M22" s="3"/>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-466000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1734000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-3552000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-2743000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-3981000</v>
       </c>
-      <c r="H23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1135,27 +1177,30 @@
       <c r="K23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L23" s="3"/>
-    </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M23" s="3"/>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>19000</v>
+      </c>
+      <c r="E24" s="3">
         <v>6000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>3000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>2000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>7000</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1165,9 +1210,12 @@
       <c r="K24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L24" s="3"/>
-    </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M24" s="3"/>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1195,27 +1243,30 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-      <c r="L25" s="3"/>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3"/>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-485000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1740000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-3555000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-2745000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-3988000</v>
       </c>
-      <c r="H26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1225,27 +1276,30 @@
       <c r="K26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L26" s="3"/>
-    </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M26" s="3"/>
+    </row>
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-434000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1683000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-3449000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-2608000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-3747000</v>
       </c>
-      <c r="H27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1255,9 +1309,12 @@
       <c r="K27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L27" s="3"/>
-    </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M27" s="3"/>
+    </row>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1285,9 +1342,12 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-      <c r="L28" s="3"/>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3"/>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1315,9 +1375,12 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3"/>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3"/>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1345,9 +1408,12 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-      <c r="L30" s="3"/>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3"/>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1375,24 +1441,27 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-      <c r="L31" s="3"/>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3"/>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-53000</v>
+      </c>
+      <c r="E32" s="3">
         <v>196000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-57000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1430000</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1405,27 +1474,30 @@
       <c r="K32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L32" s="3"/>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M32" s="3"/>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-434000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1683000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-3449000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-2608000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-3747000</v>
       </c>
-      <c r="H33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1435,9 +1507,12 @@
       <c r="K33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L33" s="3"/>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M33" s="3"/>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1465,27 +1540,30 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-      <c r="L34" s="3"/>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3"/>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-434000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1683000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-3449000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-2608000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-3747000</v>
       </c>
-      <c r="H35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1495,32 +1573,35 @@
       <c r="K35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L35" s="3"/>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M35" s="3"/>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="I38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1530,9 +1611,12 @@
       <c r="K38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="L38" s="2"/>
-    </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M38" s="2"/>
+    </row>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1545,8 +1629,9 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1559,26 +1644,27 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3138000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1448000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>4397000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1886000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1023000</v>
       </c>
-      <c r="H41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1588,27 +1674,30 @@
       <c r="K41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L41" s="3"/>
-    </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M41" s="3"/>
+    </row>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1905000</v>
+      </c>
+      <c r="E42" s="3">
         <v>3692000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>3882000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1620000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1770000</v>
       </c>
-      <c r="H42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I42" s="3" t="s">
         <v>3</v>
       </c>
@@ -1618,27 +1707,30 @@
       <c r="K42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L42" s="3"/>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M42" s="3"/>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>468000</v>
+      </c>
+      <c r="E43" s="3">
         <v>430000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>311000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>212000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>274000</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I43" s="3" t="s">
         <v>3</v>
       </c>
@@ -1648,27 +1740,30 @@
       <c r="K43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L43" s="3"/>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M43" s="3"/>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>49000</v>
+      </c>
+      <c r="E44" s="3">
         <v>48000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>4000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>3000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>5000</v>
       </c>
-      <c r="H44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I44" s="3" t="s">
         <v>3</v>
       </c>
@@ -1678,27 +1773,30 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3"/>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M44" s="3"/>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>208000</v>
+      </c>
+      <c r="E45" s="3">
         <v>70000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>81000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>34000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>68000</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I45" s="3" t="s">
         <v>3</v>
       </c>
@@ -1708,27 +1806,30 @@
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L45" s="3"/>
-    </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3"/>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5768000</v>
+      </c>
+      <c r="E46" s="3">
         <v>5688000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>8675000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3755000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3140000</v>
       </c>
-      <c r="H46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I46" s="3" t="s">
         <v>3</v>
       </c>
@@ -1738,27 +1839,30 @@
       <c r="K46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L46" s="3"/>
-    </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M46" s="3"/>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1344000</v>
+      </c>
+      <c r="E47" s="3">
         <v>2066000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1382000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>390000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>170000</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I47" s="3" t="s">
         <v>3</v>
       </c>
@@ -1768,27 +1872,30 @@
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L47" s="3"/>
-    </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M47" s="3"/>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>512000</v>
+      </c>
+      <c r="E48" s="3">
         <v>492000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>441000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>366000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>512000</v>
       </c>
-      <c r="H48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I48" s="3" t="s">
         <v>3</v>
       </c>
@@ -1798,27 +1905,30 @@
       <c r="K48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L48" s="3"/>
-    </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M48" s="3"/>
+    </row>
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>916000</v>
+      </c>
+      <c r="E49" s="3">
         <v>904000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>675000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>931000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1202000</v>
       </c>
-      <c r="H49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I49" s="3" t="s">
         <v>3</v>
       </c>
@@ -1828,9 +1938,12 @@
       <c r="K49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L49" s="3"/>
-    </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M49" s="3"/>
+    </row>
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1858,9 +1971,12 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-      <c r="L50" s="3"/>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+      <c r="M50" s="3"/>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1888,21 +2004,24 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-      <c r="L51" s="3"/>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+      <c r="M51" s="3"/>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>252000</v>
+      </c>
+      <c r="E52" s="3">
         <v>20000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>5000</v>
       </c>
-      <c r="F52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G52" s="3" t="s">
         <v>3</v>
       </c>
@@ -1918,9 +2037,12 @@
       <c r="K52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L52" s="3"/>
-    </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M52" s="3"/>
+    </row>
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1948,27 +2070,30 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-      <c r="L53" s="3"/>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+      <c r="M53" s="3"/>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8792000</v>
+      </c>
+      <c r="E54" s="3">
         <v>9170000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>11178000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>5442000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>5024000</v>
       </c>
-      <c r="H54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I54" s="3" t="s">
         <v>3</v>
       </c>
@@ -1978,9 +2103,12 @@
       <c r="K54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L54" s="3"/>
-    </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M54" s="3"/>
+    </row>
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1993,8 +2121,9 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2007,26 +2136,27 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>862000</v>
+        <v>925000</v>
       </c>
       <c r="E57" s="3">
-        <v>441000</v>
+        <v>189000</v>
       </c>
       <c r="F57" s="3">
+        <v>167000</v>
+      </c>
+      <c r="G57" s="3">
         <v>661000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>619000</v>
       </c>
-      <c r="H57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2036,27 +2166,30 @@
       <c r="K57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L57" s="3"/>
-    </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M57" s="3"/>
+    </row>
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>125000</v>
+      </c>
+      <c r="E58" s="3">
         <v>117000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>144000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>140000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>161000</v>
       </c>
-      <c r="H58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2066,27 +2199,30 @@
       <c r="K58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L58" s="3"/>
-    </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M58" s="3"/>
+    </row>
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>118000</v>
+        <v>428000</v>
       </c>
       <c r="E59" s="3">
-        <v>441000</v>
+        <v>791000</v>
       </c>
       <c r="F59" s="3">
+        <v>715000</v>
+      </c>
+      <c r="G59" s="3">
         <v>35000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>3000</v>
       </c>
-      <c r="H59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2096,27 +2232,30 @@
       <c r="K59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L59" s="3"/>
-    </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M59" s="3"/>
+    </row>
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1478000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1097000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1026000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>836000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>783000</v>
       </c>
-      <c r="H60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2126,27 +2265,30 @@
       <c r="K60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L60" s="3"/>
-    </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M60" s="3"/>
+    </row>
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>668000</v>
+      </c>
+      <c r="E61" s="3">
         <v>1248000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2031000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>10878000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>8440000</v>
       </c>
-      <c r="H61" s="3">
-        <v>0</v>
-      </c>
       <c r="I61" s="3">
         <v>0</v>
       </c>
@@ -2156,27 +2298,30 @@
       <c r="K61" s="3">
         <v>0</v>
       </c>
-      <c r="L61" s="3"/>
-    </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3"/>
+    </row>
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>178000</v>
+      </c>
+      <c r="E62" s="3">
         <v>168000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>102000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>22000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>25000</v>
       </c>
-      <c r="H62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2186,9 +2331,12 @@
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L62" s="3"/>
-    </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M62" s="3"/>
+    </row>
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2216,9 +2364,12 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-      <c r="L63" s="3"/>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+      <c r="M63" s="3"/>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2246,9 +2397,12 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-      <c r="L64" s="3"/>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+      <c r="M64" s="3"/>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2276,27 +2430,30 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-      <c r="L65" s="3"/>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+      <c r="M65" s="3"/>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2343000</v>
+      </c>
+      <c r="E66" s="3">
         <v>2567000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3445000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>11841000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>9315000</v>
       </c>
-      <c r="H66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2306,9 +2463,12 @@
       <c r="K66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L66" s="3"/>
-    </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M66" s="3"/>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2321,8 +2481,9 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2350,9 +2511,12 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-      <c r="L68" s="3"/>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+      <c r="M68" s="3"/>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2380,9 +2544,12 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-      <c r="L69" s="3"/>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+      <c r="M69" s="3"/>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2410,9 +2577,12 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-      <c r="L70" s="3"/>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3"/>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2440,27 +2610,30 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-      <c r="L71" s="3"/>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+      <c r="M71" s="3"/>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-16220000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-15675000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-13796000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-6539000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-4370000</v>
       </c>
-      <c r="H72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I72" s="3" t="s">
         <v>3</v>
       </c>
@@ -2470,9 +2643,12 @@
       <c r="K72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L72" s="3"/>
-    </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M72" s="3"/>
+    </row>
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2500,9 +2676,12 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-      <c r="L73" s="3"/>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+      <c r="M73" s="3"/>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2530,9 +2709,12 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-      <c r="L74" s="3"/>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+      <c r="M74" s="3"/>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2560,27 +2742,30 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-      <c r="L75" s="3"/>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+      <c r="M75" s="3"/>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6449000</v>
+      </c>
+      <c r="E76" s="3">
         <v>6603000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>7733000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-6399000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-4291000</v>
       </c>
-      <c r="H76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I76" s="3" t="s">
         <v>3</v>
       </c>
@@ -2590,9 +2775,12 @@
       <c r="K76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L76" s="3"/>
-    </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M76" s="3"/>
+    </row>
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2620,32 +2808,35 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-      <c r="L77" s="3"/>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+      <c r="M77" s="3"/>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="I80" s="2" t="s">
         <v>3</v>
       </c>
@@ -2655,27 +2846,30 @@
       <c r="K80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="L80" s="2"/>
-    </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M80" s="2"/>
+    </row>
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-434000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1683000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-3449000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-2608000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-3747000</v>
       </c>
-      <c r="H81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I81" s="3" t="s">
         <v>3</v>
       </c>
@@ -2685,9 +2879,12 @@
       <c r="K81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L81" s="3"/>
-    </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M81" s="3"/>
+    </row>
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2700,26 +2897,27 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>145000</v>
+      </c>
+      <c r="E83" s="3">
         <v>150000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>345000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>387000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>647000</v>
       </c>
-      <c r="H83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I83" s="3" t="s">
         <v>3</v>
       </c>
@@ -2729,9 +2927,12 @@
       <c r="K83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L83" s="3"/>
-    </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M83" s="3"/>
+    </row>
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2759,9 +2960,12 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-      <c r="L84" s="3"/>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+      <c r="M84" s="3"/>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2789,9 +2993,12 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-      <c r="L85" s="3"/>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+      <c r="M85" s="3"/>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2819,9 +3026,12 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-      <c r="L86" s="3"/>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+      <c r="M86" s="3"/>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2849,9 +3059,12 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-      <c r="L87" s="3"/>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+      <c r="M87" s="3"/>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2879,27 +3092,30 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-      <c r="L88" s="3"/>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+      <c r="M88" s="3"/>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>86000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-798000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-938000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-643000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-2112000</v>
       </c>
-      <c r="H89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I89" s="3" t="s">
         <v>3</v>
       </c>
@@ -2909,9 +3125,12 @@
       <c r="K89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L89" s="3"/>
-    </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M89" s="3"/>
+    </row>
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2924,26 +3143,27 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-71000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-58000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-73000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-22000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-98000</v>
       </c>
-      <c r="H91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I91" s="3" t="s">
         <v>3</v>
       </c>
@@ -2953,9 +3173,12 @@
       <c r="K91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L91" s="3"/>
-    </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M91" s="3"/>
+    </row>
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2983,9 +3206,12 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-      <c r="L92" s="3"/>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+      <c r="M92" s="3"/>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3013,27 +3239,30 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-      <c r="L93" s="3"/>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+      <c r="M93" s="3"/>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>1871000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1062000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2757000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-318000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>393000</v>
       </c>
-      <c r="H94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I94" s="3" t="s">
         <v>3</v>
       </c>
@@ -3043,9 +3272,12 @@
       <c r="K94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L94" s="3"/>
-    </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M94" s="3"/>
+    </row>
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3058,8 +3290,9 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3087,9 +3320,12 @@
       <c r="K96" s="3">
         <v>0</v>
       </c>
-      <c r="L96" s="3"/>
-    </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3"/>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3117,9 +3353,12 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-      <c r="L97" s="3"/>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+      <c r="M97" s="3"/>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3147,9 +3386,12 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-      <c r="L98" s="3"/>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+      <c r="M98" s="3"/>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3177,27 +3419,30 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-      <c r="L99" s="3"/>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+      <c r="M99" s="3"/>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-770000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1122000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>6566000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1578000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1951000</v>
       </c>
-      <c r="H100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I100" s="3" t="s">
         <v>3</v>
       </c>
@@ -3207,27 +3452,30 @@
       <c r="K100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L100" s="3"/>
-    </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M100" s="3"/>
+    </row>
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-57000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-37000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>15000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>12000</v>
       </c>
-      <c r="H101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I101" s="3" t="s">
         <v>3</v>
       </c>
@@ -3237,27 +3485,30 @@
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L101" s="3"/>
-    </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M101" s="3"/>
+    </row>
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1186000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-3039000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>2834000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>632000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>244000</v>
       </c>
-      <c r="H102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I102" s="3" t="s">
         <v>3</v>
       </c>
@@ -3267,7 +3518,10 @@
       <c r="K102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L102" s="3"/>
+      <c r="L102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/GRAB_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/GRAB_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="92">
   <si>
     <t>GRAB</t>
   </si>
@@ -896,7 +896,7 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>128000</v>
+        <v>127000</v>
       </c>
       <c r="E14" s="3">
         <v>54000</v>
@@ -1055,7 +1055,7 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>53000</v>
+        <v>152000</v>
       </c>
       <c r="E20" s="3">
         <v>-196000</v>
@@ -1088,7 +1088,7 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-321000</v>
+        <v>-222000</v>
       </c>
       <c r="E21" s="3">
         <v>-1419000</v>
@@ -1120,8 +1120,8 @@
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>3</v>
+      <c r="D22" s="3">
+        <v>99000</v>
       </c>
       <c r="E22" s="3">
         <v>165000</v>
@@ -1451,7 +1451,7 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-53000</v>
+        <v>-152000</v>
       </c>
       <c r="E32" s="3">
         <v>196000</v>
@@ -1651,7 +1651,7 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>3138000</v>
+        <v>2488000</v>
       </c>
       <c r="E41" s="3">
         <v>1448000</v>
@@ -1684,7 +1684,7 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>1905000</v>
+        <v>2663000</v>
       </c>
       <c r="E42" s="3">
         <v>3692000</v>
@@ -1717,7 +1717,7 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>468000</v>
+        <v>513000</v>
       </c>
       <c r="E43" s="3">
         <v>430000</v>
@@ -1783,7 +1783,7 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>208000</v>
+        <v>55000</v>
       </c>
       <c r="E45" s="3">
         <v>70000</v>
@@ -1849,7 +1849,7 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1344000</v>
+        <v>1540000</v>
       </c>
       <c r="E47" s="3">
         <v>2066000</v>
@@ -2014,7 +2014,7 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>252000</v>
+        <v>56000</v>
       </c>
       <c r="E52" s="3">
         <v>20000</v>
@@ -2143,7 +2143,7 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>925000</v>
+        <v>185000</v>
       </c>
       <c r="E57" s="3">
         <v>189000</v>
@@ -2209,7 +2209,7 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>428000</v>
+        <v>1168000</v>
       </c>
       <c r="E59" s="3">
         <v>791000</v>

--- a/AAII_Financials/Yearly/GRAB_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/GRAB_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="92">
   <si>
     <t>GRAB</t>
   </si>
@@ -662,8 +662,8 @@
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
@@ -755,10 +755,10 @@
         <v>1356000</v>
       </c>
       <c r="F9" s="3">
-        <v>1063000</v>
+        <v>1070000</v>
       </c>
       <c r="G9" s="3">
-        <v>948000</v>
+        <v>963000</v>
       </c>
       <c r="H9" s="3">
         <v>1320000</v>
@@ -788,13 +788,13 @@
         <v>77000</v>
       </c>
       <c r="F10" s="3">
-        <v>-388000</v>
+        <v>-395000</v>
       </c>
       <c r="G10" s="3">
-        <v>-479000</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
+        <v>-494000</v>
+      </c>
+      <c r="H10" s="3">
+        <v>-2165000</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>3</v>
@@ -833,7 +833,7 @@
         <v>421000</v>
       </c>
       <c r="E12" s="3">
-        <v>466000</v>
+        <v>465000</v>
       </c>
       <c r="F12" s="3">
         <v>356000</v>
@@ -896,19 +896,19 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>127000</v>
+        <v>44000</v>
       </c>
       <c r="E14" s="3">
-        <v>54000</v>
+        <v>1000</v>
       </c>
       <c r="F14" s="3">
-        <v>379000</v>
+        <v>0</v>
       </c>
       <c r="G14" s="3">
-        <v>88000</v>
+        <v>34000</v>
       </c>
       <c r="H14" s="3">
-        <v>56000</v>
+        <v>29000</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
@@ -929,19 +929,19 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>145000</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>345000</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>387000</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>647000</v>
       </c>
       <c r="I15" s="3">
         <v>0</v>
@@ -974,19 +974,19 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2878000</v>
+        <v>2834000</v>
       </c>
       <c r="E17" s="3">
-        <v>2806000</v>
+        <v>2805000</v>
       </c>
       <c r="F17" s="3">
-        <v>2583000</v>
+        <v>2230000</v>
       </c>
       <c r="G17" s="3">
-        <v>1782000</v>
+        <v>1748000</v>
       </c>
       <c r="H17" s="3">
-        <v>2165000</v>
+        <v>2136000</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>3</v>
@@ -1007,19 +1007,19 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-519000</v>
+        <v>-475000</v>
       </c>
       <c r="E18" s="3">
-        <v>-1373000</v>
+        <v>-1372000</v>
       </c>
       <c r="F18" s="3">
-        <v>-1908000</v>
+        <v>-1555000</v>
       </c>
       <c r="G18" s="3">
-        <v>-1313000</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>3</v>
+        <v>-1279000</v>
+      </c>
+      <c r="H18" s="3">
+        <v>-2981000</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>3</v>
@@ -1055,19 +1055,19 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>152000</v>
+        <v>45000</v>
       </c>
       <c r="E20" s="3">
-        <v>-196000</v>
+        <v>303000</v>
       </c>
       <c r="F20" s="3">
-        <v>57000</v>
+        <v>322000</v>
       </c>
       <c r="G20" s="3">
-        <v>-1430000</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>3</v>
+        <v>39000</v>
+      </c>
+      <c r="H20" s="3">
+        <v>-6000</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>3</v>
@@ -1088,25 +1088,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-222000</v>
+        <v>-375000</v>
       </c>
       <c r="E21" s="3">
-        <v>-1419000</v>
+        <v>-1525000</v>
       </c>
       <c r="F21" s="3">
-        <v>-1506000</v>
+        <v>-1532000</v>
       </c>
       <c r="G21" s="3">
-        <v>-2356000</v>
+        <v>-931000</v>
       </c>
       <c r="H21" s="3">
-        <v>-3334000</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
+        <v>-2328000</v>
+      </c>
+      <c r="I21" s="3">
+        <v>0</v>
+      </c>
+      <c r="J21" s="3">
+        <v>0</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>3</v>
@@ -1121,19 +1121,19 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>99000</v>
+        <v>98000</v>
       </c>
       <c r="E22" s="3">
-        <v>165000</v>
+        <v>58000</v>
       </c>
       <c r="F22" s="3">
-        <v>1701000</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>3</v>
+        <v>1675000</v>
+      </c>
+      <c r="G22" s="3">
+        <v>1433000</v>
+      </c>
+      <c r="H22" s="3">
+        <v>1053000</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>3</v>
@@ -1451,19 +1451,19 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-152000</v>
+        <v>-45000</v>
       </c>
       <c r="E32" s="3">
-        <v>196000</v>
+        <v>-303000</v>
       </c>
       <c r="F32" s="3">
-        <v>-57000</v>
+        <v>-322000</v>
       </c>
       <c r="G32" s="3">
-        <v>1430000</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>3</v>
+        <v>-39000</v>
+      </c>
+      <c r="H32" s="3">
+        <v>6000</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>3</v>
@@ -1651,19 +1651,19 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>2488000</v>
+        <v>3138000</v>
       </c>
       <c r="E41" s="3">
-        <v>1448000</v>
+        <v>1952000</v>
       </c>
       <c r="F41" s="3">
-        <v>4397000</v>
+        <v>4991000</v>
       </c>
       <c r="G41" s="3">
-        <v>1886000</v>
+        <v>2173000</v>
       </c>
       <c r="H41" s="3">
-        <v>1023000</v>
+        <v>1511000</v>
       </c>
       <c r="I41" s="3" t="s">
         <v>3</v>
@@ -1684,25 +1684,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>2663000</v>
+        <v>2001000</v>
       </c>
       <c r="E42" s="3">
-        <v>3692000</v>
+        <v>3176000</v>
       </c>
       <c r="F42" s="3">
-        <v>3882000</v>
+        <v>3288000</v>
       </c>
       <c r="G42" s="3">
-        <v>1620000</v>
+        <v>1333000</v>
       </c>
       <c r="H42" s="3">
-        <v>1770000</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>3</v>
+        <v>1282000</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
+        <v>0</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>3</v>
@@ -1717,19 +1717,19 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>513000</v>
+        <v>498000</v>
       </c>
       <c r="E43" s="3">
-        <v>430000</v>
+        <v>418000</v>
       </c>
       <c r="F43" s="3">
-        <v>311000</v>
+        <v>303000</v>
       </c>
       <c r="G43" s="3">
-        <v>212000</v>
+        <v>197000</v>
       </c>
       <c r="H43" s="3">
-        <v>274000</v>
+        <v>240000</v>
       </c>
       <c r="I43" s="3" t="s">
         <v>3</v>
@@ -1783,19 +1783,19 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>55000</v>
+        <v>27000</v>
       </c>
       <c r="E45" s="3">
-        <v>70000</v>
+        <v>24000</v>
       </c>
       <c r="F45" s="3">
-        <v>81000</v>
+        <v>23000</v>
       </c>
       <c r="G45" s="3">
+        <v>28000</v>
+      </c>
+      <c r="H45" s="3">
         <v>34000</v>
-      </c>
-      <c r="H45" s="3">
-        <v>68000</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>3</v>
@@ -1849,19 +1849,19 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1540000</v>
+        <v>1290000</v>
       </c>
       <c r="E47" s="3">
-        <v>2066000</v>
+        <v>1849000</v>
       </c>
       <c r="F47" s="3">
-        <v>1382000</v>
+        <v>1255000</v>
       </c>
       <c r="G47" s="3">
-        <v>390000</v>
+        <v>386000</v>
       </c>
       <c r="H47" s="3">
-        <v>170000</v>
+        <v>165000</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>3</v>
@@ -1891,10 +1891,10 @@
         <v>441000</v>
       </c>
       <c r="G48" s="3">
-        <v>366000</v>
+        <v>384000</v>
       </c>
       <c r="H48" s="3">
-        <v>512000</v>
+        <v>534000</v>
       </c>
       <c r="I48" s="3" t="s">
         <v>3</v>
@@ -1924,10 +1924,10 @@
         <v>675000</v>
       </c>
       <c r="G49" s="3">
-        <v>931000</v>
+        <v>913000</v>
       </c>
       <c r="H49" s="3">
-        <v>1202000</v>
+        <v>1180000</v>
       </c>
       <c r="I49" s="3" t="s">
         <v>3</v>
@@ -2014,19 +2014,19 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>56000</v>
+        <v>102000</v>
       </c>
       <c r="E52" s="3">
-        <v>20000</v>
+        <v>130000</v>
       </c>
       <c r="F52" s="3">
+        <v>127000</v>
+      </c>
+      <c r="G52" s="3">
+        <v>4000</v>
+      </c>
+      <c r="H52" s="3">
         <v>5000</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>3</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>3</v>
@@ -2152,10 +2152,10 @@
         <v>167000</v>
       </c>
       <c r="G57" s="3">
-        <v>661000</v>
+        <v>109000</v>
       </c>
       <c r="H57" s="3">
-        <v>619000</v>
+        <v>99000</v>
       </c>
       <c r="I57" s="3" t="s">
         <v>3</v>
@@ -2209,19 +2209,19 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1168000</v>
+        <v>766000</v>
       </c>
       <c r="E59" s="3">
-        <v>791000</v>
+        <v>384000</v>
       </c>
       <c r="F59" s="3">
-        <v>715000</v>
+        <v>341000</v>
       </c>
       <c r="G59" s="3">
-        <v>35000</v>
+        <v>289000</v>
       </c>
       <c r="H59" s="3">
-        <v>3000</v>
+        <v>216000</v>
       </c>
       <c r="I59" s="3" t="s">
         <v>3</v>
@@ -2308,19 +2308,19 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>178000</v>
+        <v>147000</v>
       </c>
       <c r="E62" s="3">
-        <v>168000</v>
+        <v>137000</v>
       </c>
       <c r="F62" s="3">
-        <v>102000</v>
+        <v>84000</v>
       </c>
       <c r="G62" s="3">
-        <v>22000</v>
+        <v>6000</v>
       </c>
       <c r="H62" s="3">
-        <v>25000</v>
+        <v>9000</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>3</v>
@@ -2440,19 +2440,19 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>2343000</v>
+        <v>2324000</v>
       </c>
       <c r="E66" s="3">
-        <v>2567000</v>
+        <v>2513000</v>
       </c>
       <c r="F66" s="3">
-        <v>3445000</v>
+        <v>3159000</v>
       </c>
       <c r="G66" s="3">
-        <v>11841000</v>
+        <v>11736000</v>
       </c>
       <c r="H66" s="3">
-        <v>9315000</v>
+        <v>9248000</v>
       </c>
       <c r="I66" s="3" t="s">
         <v>3</v>
@@ -2620,19 +2620,19 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-16220000</v>
+        <v>-16764000</v>
       </c>
       <c r="E72" s="3">
-        <v>-15675000</v>
+        <v>-16277000</v>
       </c>
       <c r="F72" s="3">
-        <v>-13796000</v>
+        <v>-14402000</v>
       </c>
       <c r="G72" s="3">
-        <v>-6539000</v>
+        <v>-10490000</v>
       </c>
       <c r="H72" s="3">
-        <v>-4370000</v>
+        <v>-7982000</v>
       </c>
       <c r="I72" s="3" t="s">
         <v>3</v>
@@ -2904,19 +2904,19 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>145000</v>
+        <v>128000</v>
       </c>
       <c r="E83" s="3">
-        <v>150000</v>
+        <v>129000</v>
       </c>
       <c r="F83" s="3">
-        <v>345000</v>
+        <v>109000</v>
       </c>
       <c r="G83" s="3">
-        <v>387000</v>
+        <v>126000</v>
       </c>
       <c r="H83" s="3">
-        <v>647000</v>
+        <v>109000</v>
       </c>
       <c r="I83" s="3" t="s">
         <v>3</v>
@@ -3108,7 +3108,7 @@
         <v>-798000</v>
       </c>
       <c r="F89" s="3">
-        <v>-938000</v>
+        <v>-954000</v>
       </c>
       <c r="G89" s="3">
         <v>-643000</v>
@@ -3258,7 +3258,7 @@
         <v>-2757000</v>
       </c>
       <c r="G94" s="3">
-        <v>-318000</v>
+        <v>-288000</v>
       </c>
       <c r="H94" s="3">
         <v>393000</v>
@@ -3501,19 +3501,19 @@
         <v>-3039000</v>
       </c>
       <c r="F102" s="3">
-        <v>2834000</v>
+        <v>2818000</v>
       </c>
       <c r="G102" s="3">
-        <v>632000</v>
+        <v>662000</v>
       </c>
       <c r="H102" s="3">
         <v>244000</v>
       </c>
-      <c r="I102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J102" s="3" t="s">
-        <v>3</v>
+      <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
+        <v>0</v>
       </c>
       <c r="K102" s="3" t="s">
         <v>3</v>

--- a/AAII_Financials/Yearly/GRAB_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/GRAB_YR_FIN.xlsx
@@ -656,50 +656,50 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="8" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="J7" s="2" t="s">
         <v>3</v>
       </c>
@@ -709,27 +709,30 @@
       <c r="L7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="M7" s="2"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N7" s="2"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>2797000</v>
+      </c>
+      <c r="E8" s="3">
         <v>2359000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1433000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>675000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>469000</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I8" s="3" t="s">
         <v>3</v>
       </c>
@@ -742,30 +745,33 @@
       <c r="L8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M8" s="3"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N8" s="3"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>1499000</v>
+        <v>1679000</v>
       </c>
       <c r="E9" s="3">
-        <v>1356000</v>
+        <v>1541000</v>
       </c>
       <c r="F9" s="3">
+        <v>1387000</v>
+      </c>
+      <c r="G9" s="3">
         <v>1070000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>963000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1320000</v>
       </c>
-      <c r="I9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J9" s="3" t="s">
         <v>3</v>
       </c>
@@ -775,30 +781,33 @@
       <c r="L9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M9" s="3"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N9" s="3"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>860000</v>
+        <v>1118000</v>
       </c>
       <c r="E10" s="3">
-        <v>77000</v>
+        <v>818000</v>
       </c>
       <c r="F10" s="3">
+        <v>46000</v>
+      </c>
+      <c r="G10" s="3">
         <v>-395000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-494000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-2165000</v>
       </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J10" s="3" t="s">
         <v>3</v>
       </c>
@@ -808,9 +817,12 @@
       <c r="L10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M10" s="3"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N10" s="3"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -824,29 +836,30 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>410000</v>
+      </c>
+      <c r="E12" s="3">
         <v>421000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>465000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>356000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>257000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>231000</v>
       </c>
-      <c r="I12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J12" s="3" t="s">
         <v>3</v>
       </c>
@@ -856,9 +869,12 @@
       <c r="L12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M12" s="3"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N12" s="3"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -889,30 +905,33 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-      <c r="M13" s="3"/>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+      <c r="N13" s="3"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>44000</v>
+        <v>4000</v>
       </c>
       <c r="E14" s="3">
-        <v>1000</v>
+        <v>83000</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
+        <v>298000</v>
       </c>
       <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
         <v>34000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>29000</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
@@ -922,30 +941,33 @@
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" s="3"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>147000</v>
+      </c>
+      <c r="E15" s="3">
         <v>145000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>150000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>345000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>387000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>647000</v>
       </c>
-      <c r="I15" s="3">
-        <v>0</v>
-      </c>
       <c r="J15" s="3">
         <v>0</v>
       </c>
@@ -955,9 +977,12 @@
       <c r="L15" s="3">
         <v>0</v>
       </c>
-      <c r="M15" s="3"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M15" s="3">
+        <v>0</v>
+      </c>
+      <c r="N15" s="3"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -968,29 +993,30 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2834000</v>
+        <v>2953000</v>
       </c>
       <c r="E17" s="3">
-        <v>2805000</v>
+        <v>2830000</v>
       </c>
       <c r="F17" s="3">
+        <v>2795000</v>
+      </c>
+      <c r="G17" s="3">
         <v>2230000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1748000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2136000</v>
       </c>
-      <c r="I17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1000,30 +1026,33 @@
       <c r="L17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M17" s="3"/>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N17" s="3"/>
+    </row>
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-475000</v>
+        <v>-156000</v>
       </c>
       <c r="E18" s="3">
-        <v>-1372000</v>
+        <v>-471000</v>
       </c>
       <c r="F18" s="3">
+        <v>-1362000</v>
+      </c>
+      <c r="G18" s="3">
         <v>-1555000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-1279000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-2981000</v>
       </c>
-      <c r="I18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1033,9 +1062,12 @@
       <c r="L18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M18" s="3"/>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N18" s="3"/>
+    </row>
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1049,29 +1081,30 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>45000</v>
+        <v>81000</v>
       </c>
       <c r="E20" s="3">
-        <v>303000</v>
+        <v>10000</v>
       </c>
       <c r="F20" s="3">
+        <v>16000</v>
+      </c>
+      <c r="G20" s="3">
         <v>322000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>39000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-6000</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1081,63 +1114,69 @@
       <c r="L20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M20" s="3"/>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N20" s="3"/>
+    </row>
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-375000</v>
+        <v>-90000</v>
       </c>
       <c r="E21" s="3">
-        <v>-1525000</v>
+        <v>-336000</v>
       </c>
       <c r="F21" s="3">
+        <v>-1228000</v>
+      </c>
+      <c r="G21" s="3">
         <v>-1532000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-931000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-2328000</v>
       </c>
-      <c r="I21" s="3">
-        <v>0</v>
-      </c>
       <c r="J21" s="3">
         <v>0</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
+      <c r="K21" s="3">
+        <v>0</v>
       </c>
       <c r="L21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M21" s="3"/>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N21" s="3"/>
+    </row>
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>98000</v>
+        <v>41000</v>
       </c>
       <c r="E22" s="3">
-        <v>58000</v>
+        <v>99000</v>
       </c>
       <c r="F22" s="3">
+        <v>165000</v>
+      </c>
+      <c r="G22" s="3">
         <v>1675000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>1433000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>1053000</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1147,30 +1186,33 @@
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M22" s="3"/>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N22" s="3"/>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-95000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-466000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1734000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-3552000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-2743000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-3981000</v>
       </c>
-      <c r="I23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1180,30 +1222,33 @@
       <c r="L23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M23" s="3"/>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N23" s="3"/>
+    </row>
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>63000</v>
+      </c>
+      <c r="E24" s="3">
         <v>19000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>6000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>3000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>2000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>7000</v>
       </c>
-      <c r="I24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1213,9 +1258,12 @@
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M24" s="3"/>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N24" s="3"/>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1246,30 +1294,33 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-      <c r="M25" s="3"/>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+      <c r="N25" s="3"/>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-158000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-485000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1740000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-3555000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-2745000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-3988000</v>
       </c>
-      <c r="I26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1279,30 +1330,33 @@
       <c r="L26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M26" s="3"/>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N26" s="3"/>
+    </row>
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-105000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-434000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1683000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-3449000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-2608000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-3747000</v>
       </c>
-      <c r="I27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1312,9 +1366,12 @@
       <c r="L27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M27" s="3"/>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N27" s="3"/>
+    </row>
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1345,9 +1402,12 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-      <c r="M28" s="3"/>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+      <c r="N28" s="3"/>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1378,9 +1438,12 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-      <c r="M29" s="3"/>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3"/>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1411,9 +1474,12 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-      <c r="M30" s="3"/>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+      <c r="N30" s="3"/>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1444,30 +1510,33 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-      <c r="M31" s="3"/>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+      <c r="N31" s="3"/>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-45000</v>
+        <v>-81000</v>
       </c>
       <c r="E32" s="3">
-        <v>-303000</v>
+        <v>-10000</v>
       </c>
       <c r="F32" s="3">
+        <v>-16000</v>
+      </c>
+      <c r="G32" s="3">
         <v>-322000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-39000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>6000</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1477,30 +1546,33 @@
       <c r="L32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M32" s="3"/>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N32" s="3"/>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-105000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-434000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1683000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-3449000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-2608000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-3747000</v>
       </c>
-      <c r="I33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1510,9 +1582,12 @@
       <c r="L33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M33" s="3"/>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N33" s="3"/>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1543,30 +1618,33 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-      <c r="M34" s="3"/>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+      <c r="N34" s="3"/>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-105000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-434000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1683000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-3449000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-2608000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-3747000</v>
       </c>
-      <c r="I35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1576,35 +1654,38 @@
       <c r="L35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M35" s="3"/>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N35" s="3"/>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="J38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1614,9 +1695,12 @@
       <c r="L38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="M38" s="2"/>
-    </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N38" s="2"/>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1630,8 +1714,9 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1645,29 +1730,30 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2964000</v>
+      </c>
+      <c r="E41" s="3">
         <v>3138000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1952000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4991000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2173000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1511000</v>
       </c>
-      <c r="I41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1677,63 +1763,69 @@
       <c r="L41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M41" s="3"/>
-    </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N41" s="3"/>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>2001000</v>
+        <v>2714000</v>
       </c>
       <c r="E42" s="3">
+        <v>2013000</v>
+      </c>
+      <c r="F42" s="3">
         <v>3176000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>3288000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1333000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1282000</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
         <v>0</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>3</v>
+      <c r="K42" s="3">
+        <v>0</v>
       </c>
       <c r="L42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M42" s="3"/>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N42" s="3"/>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>663000</v>
+      </c>
+      <c r="E43" s="3">
         <v>498000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>418000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>303000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>197000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>240000</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J43" s="3" t="s">
         <v>3</v>
       </c>
@@ -1743,30 +1835,33 @@
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M43" s="3"/>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N43" s="3"/>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>59000</v>
+      </c>
+      <c r="E44" s="3">
         <v>49000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>48000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>4000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>3000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>5000</v>
       </c>
-      <c r="I44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
@@ -1776,30 +1871,33 @@
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M44" s="3"/>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N44" s="3"/>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>27000</v>
+        <v>81000</v>
       </c>
       <c r="E45" s="3">
+        <v>15000</v>
+      </c>
+      <c r="F45" s="3">
         <v>24000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>23000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>28000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>34000</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
@@ -1809,30 +1907,33 @@
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M45" s="3"/>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N45" s="3"/>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>6566000</v>
+      </c>
+      <c r="E46" s="3">
         <v>5768000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>5688000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>8675000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3755000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>3140000</v>
       </c>
-      <c r="I46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J46" s="3" t="s">
         <v>3</v>
       </c>
@@ -1842,30 +1943,33 @@
       <c r="L46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M46" s="3"/>
-    </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N46" s="3"/>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>896000</v>
+      </c>
+      <c r="E47" s="3">
         <v>1290000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1849000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1255000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>386000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>165000</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
@@ -1875,30 +1979,33 @@
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M47" s="3"/>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N47" s="3"/>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>567000</v>
+      </c>
+      <c r="E48" s="3">
         <v>512000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>492000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>441000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>384000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>534000</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J48" s="3" t="s">
         <v>3</v>
       </c>
@@ -1908,30 +2015,33 @@
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M48" s="3"/>
-    </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N48" s="3"/>
+    </row>
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>975000</v>
+      </c>
+      <c r="E49" s="3">
         <v>916000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>904000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>675000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>913000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1180000</v>
       </c>
-      <c r="I49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J49" s="3" t="s">
         <v>3</v>
       </c>
@@ -1941,9 +2051,12 @@
       <c r="L49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M49" s="3"/>
-    </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N49" s="3"/>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1974,9 +2087,12 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-      <c r="M50" s="3"/>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+      <c r="N50" s="3"/>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2007,30 +2123,33 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-      <c r="M51" s="3"/>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+      <c r="N51" s="3"/>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>119000</v>
+      </c>
+      <c r="E52" s="3">
         <v>102000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>130000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>127000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>4000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>5000</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2040,9 +2159,12 @@
       <c r="L52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M52" s="3"/>
-    </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N52" s="3"/>
+    </row>
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2073,30 +2195,33 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-      <c r="M53" s="3"/>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+      <c r="N53" s="3"/>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>9295000</v>
+      </c>
+      <c r="E54" s="3">
         <v>8792000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>9170000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>11178000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>5442000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>5024000</v>
       </c>
-      <c r="I54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2106,9 +2231,12 @@
       <c r="L54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M54" s="3"/>
-    </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N54" s="3"/>
+    </row>
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2122,8 +2250,9 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2137,29 +2266,30 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>208000</v>
+      </c>
+      <c r="E57" s="3">
         <v>185000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>189000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>167000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>109000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>99000</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2169,30 +2299,33 @@
       <c r="L57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M57" s="3"/>
-    </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N57" s="3"/>
+    </row>
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>123000</v>
+      </c>
+      <c r="E58" s="3">
         <v>125000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>117000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>144000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>140000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>161000</v>
       </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2202,30 +2335,33 @@
       <c r="L58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M58" s="3"/>
-    </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N58" s="3"/>
+    </row>
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1738000</v>
+      </c>
+      <c r="E59" s="3">
         <v>766000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>384000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>341000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>289000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>216000</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2235,30 +2371,33 @@
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M59" s="3"/>
-    </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N59" s="3"/>
+    </row>
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2592000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1478000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1097000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1026000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>836000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>783000</v>
       </c>
-      <c r="I60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2268,30 +2407,33 @@
       <c r="L60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M60" s="3"/>
-    </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N60" s="3"/>
+    </row>
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>241000</v>
+      </c>
+      <c r="E61" s="3">
         <v>668000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1248000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2031000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>10878000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>8440000</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
         <v>0</v>
       </c>
@@ -2301,30 +2443,33 @@
       <c r="L61" s="3">
         <v>0</v>
       </c>
-      <c r="M61" s="3"/>
-    </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3"/>
+    </row>
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>74000</v>
+      </c>
+      <c r="E62" s="3">
         <v>147000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>137000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>84000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>6000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>9000</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2334,9 +2479,12 @@
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M62" s="3"/>
-    </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N62" s="3"/>
+    </row>
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2367,9 +2515,12 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-      <c r="M63" s="3"/>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+      <c r="N63" s="3"/>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2400,9 +2551,12 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-      <c r="M64" s="3"/>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+      <c r="N64" s="3"/>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2433,30 +2587,33 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-      <c r="M65" s="3"/>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+      <c r="N65" s="3"/>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2944000</v>
+      </c>
+      <c r="E66" s="3">
         <v>2324000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2513000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3159000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>11736000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>9248000</v>
       </c>
-      <c r="I66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2466,9 +2623,12 @@
       <c r="L66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M66" s="3"/>
-    </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N66" s="3"/>
+    </row>
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2482,8 +2642,9 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2514,9 +2675,12 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-      <c r="M68" s="3"/>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+      <c r="N68" s="3"/>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2547,9 +2711,12 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-      <c r="M69" s="3"/>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+      <c r="N69" s="3"/>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2580,9 +2747,12 @@
       <c r="L70" s="3">
         <v>0</v>
       </c>
-      <c r="M70" s="3"/>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3"/>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2613,30 +2783,33 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-      <c r="M71" s="3"/>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+      <c r="N71" s="3"/>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-17347000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-16764000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-16277000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-14402000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-10490000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-7982000</v>
       </c>
-      <c r="I72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J72" s="3" t="s">
         <v>3</v>
       </c>
@@ -2646,9 +2819,12 @@
       <c r="L72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M72" s="3"/>
-    </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N72" s="3"/>
+    </row>
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2679,9 +2855,12 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-      <c r="M73" s="3"/>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+      <c r="N73" s="3"/>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2712,9 +2891,12 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-      <c r="M74" s="3"/>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+      <c r="N74" s="3"/>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2745,30 +2927,33 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-      <c r="M75" s="3"/>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+      <c r="N75" s="3"/>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6399000</v>
+      </c>
+      <c r="E76" s="3">
         <v>6449000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>6603000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>7733000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-6399000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-4291000</v>
       </c>
-      <c r="I76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J76" s="3" t="s">
         <v>3</v>
       </c>
@@ -2778,9 +2963,12 @@
       <c r="L76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M76" s="3"/>
-    </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N76" s="3"/>
+    </row>
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2811,35 +2999,38 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-      <c r="M77" s="3"/>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+      <c r="N77" s="3"/>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="J80" s="2" t="s">
         <v>3</v>
       </c>
@@ -2849,30 +3040,33 @@
       <c r="L80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="M80" s="2"/>
-    </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N80" s="2"/>
+    </row>
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-105000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-434000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1683000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-3449000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-2608000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-3747000</v>
       </c>
-      <c r="I81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J81" s="3" t="s">
         <v>3</v>
       </c>
@@ -2882,9 +3076,12 @@
       <c r="L81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M81" s="3"/>
-    </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N81" s="3"/>
+    </row>
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2898,29 +3095,30 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>122000</v>
+      </c>
+      <c r="E83" s="3">
         <v>128000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>129000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>109000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>126000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>109000</v>
       </c>
-      <c r="I83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J83" s="3" t="s">
         <v>3</v>
       </c>
@@ -2930,9 +3128,12 @@
       <c r="L83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M83" s="3"/>
-    </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N83" s="3"/>
+    </row>
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2963,9 +3164,12 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-      <c r="M84" s="3"/>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+      <c r="N84" s="3"/>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2996,9 +3200,12 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-      <c r="M85" s="3"/>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+      <c r="N85" s="3"/>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3029,9 +3236,12 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-      <c r="M86" s="3"/>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+      <c r="N86" s="3"/>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3062,9 +3272,12 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-      <c r="M87" s="3"/>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+      <c r="N87" s="3"/>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3095,30 +3308,33 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-      <c r="M88" s="3"/>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+      <c r="N88" s="3"/>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>852000</v>
+      </c>
+      <c r="E89" s="3">
         <v>86000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-798000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-954000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-643000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-2112000</v>
       </c>
-      <c r="I89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3128,9 +3344,12 @@
       <c r="L89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M89" s="3"/>
-    </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N89" s="3"/>
+    </row>
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3144,29 +3363,30 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-77000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-71000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-58000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-73000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-22000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-98000</v>
       </c>
-      <c r="I91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J91" s="3" t="s">
         <v>3</v>
       </c>
@@ -3176,9 +3396,12 @@
       <c r="L91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M91" s="3"/>
-    </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N91" s="3"/>
+    </row>
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3209,9 +3432,12 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-      <c r="M92" s="3"/>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+      <c r="N92" s="3"/>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3242,30 +3468,33 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-      <c r="M93" s="3"/>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+      <c r="N93" s="3"/>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-231000</v>
+      </c>
+      <c r="E94" s="3">
         <v>1871000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1062000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2757000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-288000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>393000</v>
       </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J94" s="3" t="s">
         <v>3</v>
       </c>
@@ -3275,9 +3504,12 @@
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M94" s="3"/>
-    </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N94" s="3"/>
+    </row>
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3291,8 +3523,9 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3323,9 +3556,12 @@
       <c r="L96" s="3">
         <v>0</v>
       </c>
-      <c r="M96" s="3"/>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3"/>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3356,9 +3592,12 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-      <c r="M97" s="3"/>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+      <c r="N97" s="3"/>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3389,9 +3628,12 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-      <c r="M98" s="3"/>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+      <c r="N98" s="3"/>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3422,30 +3664,33 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-      <c r="M99" s="3"/>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+      <c r="N99" s="3"/>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-771000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-770000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1122000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>6566000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1578000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1951000</v>
       </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J100" s="3" t="s">
         <v>3</v>
       </c>
@@ -3455,30 +3700,33 @@
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M100" s="3"/>
-    </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N100" s="3"/>
+    </row>
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-24000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-57000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-37000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>15000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>12000</v>
       </c>
-      <c r="I101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
@@ -3488,40 +3736,46 @@
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M101" s="3"/>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N101" s="3"/>
+    </row>
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-174000</v>
+      </c>
+      <c r="E102" s="3">
         <v>1186000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-3039000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>2818000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>662000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>244000</v>
       </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
       <c r="J102" s="3">
         <v>0</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
+      <c r="K102" s="3">
+        <v>0</v>
       </c>
       <c r="L102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M102" s="3"/>
+      <c r="M102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/GRAB_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/GRAB_YR_FIN.xlsx
@@ -924,7 +924,7 @@
         <v>298000</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
+        <v>-37000</v>
       </c>
       <c r="H14" s="3">
         <v>34000</v>
@@ -1097,7 +1097,7 @@
         <v>16000</v>
       </c>
       <c r="G20" s="3">
-        <v>322000</v>
+        <v>359000</v>
       </c>
       <c r="H20" s="3">
         <v>39000</v>
@@ -1133,7 +1133,7 @@
         <v>-1228000</v>
       </c>
       <c r="G21" s="3">
-        <v>-1532000</v>
+        <v>-1569000</v>
       </c>
       <c r="H21" s="3">
         <v>-931000</v>
@@ -1529,7 +1529,7 @@
         <v>-16000</v>
       </c>
       <c r="G32" s="3">
-        <v>-322000</v>
+        <v>-359000</v>
       </c>
       <c r="H32" s="3">
         <v>-39000</v>

--- a/AAII_Financials/Yearly/GRAB_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/GRAB_YR_FIN.xlsx
@@ -656,53 +656,53 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="8" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="9" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="K7" s="2" t="s">
         <v>3</v>
       </c>
@@ -712,30 +712,33 @@
       <c r="M7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="N7" s="2"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O7" s="2"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>3370000</v>
+      </c>
+      <c r="E8" s="3">
         <v>2797000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2359000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1433000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>675000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>469000</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J8" s="3" t="s">
         <v>3</v>
       </c>
@@ -748,33 +751,36 @@
       <c r="M8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N8" s="3"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O8" s="3"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>2033000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1679000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1541000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1387000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1070000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>963000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1320000</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K9" s="3" t="s">
         <v>3</v>
       </c>
@@ -784,33 +790,36 @@
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N9" s="3"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O9" s="3"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1337000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1118000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>818000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>46000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-395000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-494000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-2165000</v>
       </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
       </c>
@@ -820,9 +829,12 @@
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N10" s="3"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O10" s="3"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -837,32 +849,33 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>428000</v>
+      </c>
+      <c r="E12" s="3">
         <v>410000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>421000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>465000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>356000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>257000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>231000</v>
       </c>
-      <c r="J12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K12" s="3" t="s">
         <v>3</v>
       </c>
@@ -872,9 +885,12 @@
       <c r="M12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N12" s="3"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O12" s="3"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -908,33 +924,36 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-      <c r="N13" s="3"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+      <c r="O13" s="3"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-21000</v>
+      </c>
+      <c r="E14" s="3">
         <v>4000</v>
       </c>
-      <c r="E14" s="3">
-        <v>83000</v>
-      </c>
       <c r="F14" s="3">
+        <v>84000</v>
+      </c>
+      <c r="G14" s="3">
         <v>298000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-37000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>34000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>29000</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
@@ -944,33 +963,36 @@
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N14" s="3"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O14" s="3"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>177000</v>
+      </c>
+      <c r="E15" s="3">
         <v>147000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>145000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>150000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>345000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>387000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>647000</v>
       </c>
-      <c r="J15" s="3">
-        <v>0</v>
-      </c>
       <c r="K15" s="3">
         <v>0</v>
       </c>
@@ -980,9 +1002,12 @@
       <c r="M15" s="3">
         <v>0</v>
       </c>
-      <c r="N15" s="3"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N15" s="3">
+        <v>0</v>
+      </c>
+      <c r="O15" s="3"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -994,32 +1019,33 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3290000</v>
+      </c>
+      <c r="E17" s="3">
         <v>2953000</v>
       </c>
-      <c r="E17" s="3">
-        <v>2830000</v>
-      </c>
       <c r="F17" s="3">
+        <v>2829000</v>
+      </c>
+      <c r="G17" s="3">
         <v>2795000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2230000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1748000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2136000</v>
       </c>
-      <c r="J17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1029,33 +1055,36 @@
       <c r="M17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N17" s="3"/>
-    </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O17" s="3"/>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>80000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-156000</v>
       </c>
-      <c r="E18" s="3">
-        <v>-471000</v>
-      </c>
       <c r="F18" s="3">
+        <v>-470000</v>
+      </c>
+      <c r="G18" s="3">
         <v>-1362000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-1555000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-1279000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-2981000</v>
       </c>
-      <c r="J18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1065,9 +1094,12 @@
       <c r="M18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N18" s="3"/>
-    </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O18" s="3"/>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1082,32 +1114,33 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-72000</v>
+      </c>
+      <c r="E20" s="3">
         <v>81000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>10000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>16000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>359000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>39000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-6000</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1117,69 +1150,75 @@
       <c r="M20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N20" s="3"/>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O20" s="3"/>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>329000</v>
+      </c>
+      <c r="E21" s="3">
         <v>-90000</v>
       </c>
-      <c r="E21" s="3">
-        <v>-336000</v>
-      </c>
       <c r="F21" s="3">
+        <v>-335000</v>
+      </c>
+      <c r="G21" s="3">
         <v>-1228000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-1569000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-931000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-2328000</v>
       </c>
-      <c r="J21" s="3">
-        <v>0</v>
-      </c>
       <c r="K21" s="3">
         <v>0</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
+      <c r="L21" s="3">
+        <v>0</v>
       </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N21" s="3"/>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O21" s="3"/>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>71000</v>
+      </c>
+      <c r="E22" s="3">
         <v>41000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>99000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>165000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>1675000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>1433000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1053000</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1189,33 +1228,36 @@
       <c r="M22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N22" s="3"/>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O22" s="3"/>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>269000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-95000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-466000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1734000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-3552000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-2743000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-3981000</v>
       </c>
-      <c r="J23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1225,33 +1267,36 @@
       <c r="M23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N23" s="3"/>
-    </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O23" s="3"/>
+    </row>
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>69000</v>
+      </c>
+      <c r="E24" s="3">
         <v>63000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>19000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>6000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>3000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>2000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>7000</v>
       </c>
-      <c r="J24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1261,9 +1306,12 @@
       <c r="M24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N24" s="3"/>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O24" s="3"/>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1297,33 +1345,36 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-      <c r="N25" s="3"/>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+      <c r="O25" s="3"/>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>200000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-158000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-485000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1740000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-3555000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-2745000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-3988000</v>
       </c>
-      <c r="J26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1333,33 +1384,36 @@
       <c r="M26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N26" s="3"/>
-    </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O26" s="3"/>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>268000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-105000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-434000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1683000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-3449000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-2608000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-3747000</v>
       </c>
-      <c r="J27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1369,9 +1423,12 @@
       <c r="M27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N27" s="3"/>
-    </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O27" s="3"/>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1405,9 +1462,12 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-      <c r="N28" s="3"/>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+      <c r="O28" s="3"/>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1441,9 +1501,12 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-      <c r="N29" s="3"/>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3"/>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1477,9 +1540,12 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-      <c r="N30" s="3"/>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+      <c r="O30" s="3"/>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1513,33 +1579,36 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-      <c r="N31" s="3"/>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+      <c r="O31" s="3"/>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>72000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-81000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-10000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-16000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-359000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-39000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>6000</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1549,33 +1618,36 @@
       <c r="M32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N32" s="3"/>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O32" s="3"/>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>268000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-105000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-434000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-1683000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-3449000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-2608000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-3747000</v>
       </c>
-      <c r="J33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1585,9 +1657,12 @@
       <c r="M33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N33" s="3"/>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O33" s="3"/>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1621,33 +1696,36 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-      <c r="N34" s="3"/>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+      <c r="O34" s="3"/>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>268000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-105000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-434000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-1683000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-3449000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-2608000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-3747000</v>
       </c>
-      <c r="J35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1657,38 +1735,41 @@
       <c r="M35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N35" s="3"/>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O35" s="3"/>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="K38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1698,9 +1779,12 @@
       <c r="M38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="N38" s="2"/>
-    </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O38" s="2"/>
+    </row>
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1715,8 +1799,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1731,32 +1816,33 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3433000</v>
+      </c>
+      <c r="E41" s="3">
         <v>2964000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3138000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1952000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>4991000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2173000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1511000</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1766,69 +1852,75 @@
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N41" s="3"/>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O41" s="3"/>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>3428000</v>
+      </c>
+      <c r="E42" s="3">
         <v>2714000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>2013000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>3176000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>3288000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1333000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1282000</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
       <c r="K42" s="3">
         <v>0</v>
       </c>
-      <c r="L42" s="3" t="s">
-        <v>3</v>
+      <c r="L42" s="3">
+        <v>0</v>
       </c>
       <c r="M42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N42" s="3"/>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O42" s="3"/>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1034000</v>
+      </c>
+      <c r="E43" s="3">
         <v>663000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>498000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>418000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>303000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>197000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>240000</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
       </c>
@@ -1838,33 +1930,36 @@
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N43" s="3"/>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O43" s="3"/>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>87000</v>
+      </c>
+      <c r="E44" s="3">
         <v>59000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>49000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>48000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>4000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>3000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>5000</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
@@ -1874,33 +1969,36 @@
       <c r="M44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N44" s="3"/>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O44" s="3"/>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>11000</v>
+      </c>
+      <c r="E45" s="3">
         <v>81000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>15000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>24000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>23000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>28000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>34000</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
@@ -1910,33 +2008,36 @@
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N45" s="3"/>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O45" s="3"/>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>8080000</v>
+      </c>
+      <c r="E46" s="3">
         <v>6566000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>5768000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5688000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>8675000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>3755000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3140000</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K46" s="3" t="s">
         <v>3</v>
       </c>
@@ -1946,33 +2047,36 @@
       <c r="M46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N46" s="3"/>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O46" s="3"/>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1332000</v>
+      </c>
+      <c r="E47" s="3">
         <v>896000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1290000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1849000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1255000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>386000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>165000</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
@@ -1982,33 +2086,36 @@
       <c r="M47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N47" s="3"/>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O47" s="3"/>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>831000</v>
+      </c>
+      <c r="E48" s="3">
         <v>567000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>512000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>492000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>441000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>384000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>534000</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2018,33 +2125,36 @@
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N48" s="3"/>
-    </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O48" s="3"/>
+    </row>
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1057000</v>
+      </c>
+      <c r="E49" s="3">
         <v>975000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>916000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>904000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>675000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>913000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1180000</v>
       </c>
-      <c r="J49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2054,9 +2164,12 @@
       <c r="M49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N49" s="3"/>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O49" s="3"/>
+    </row>
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2090,9 +2203,12 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-      <c r="N50" s="3"/>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+      <c r="O50" s="3"/>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2126,33 +2242,36 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-      <c r="N51" s="3"/>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+      <c r="O51" s="3"/>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>178000</v>
+      </c>
+      <c r="E52" s="3">
         <v>119000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>102000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>130000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>127000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>4000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>5000</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2162,9 +2281,12 @@
       <c r="M52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N52" s="3"/>
-    </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O52" s="3"/>
+    </row>
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2198,33 +2320,36 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-      <c r="N53" s="3"/>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+      <c r="O53" s="3"/>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>11983000</v>
+      </c>
+      <c r="E54" s="3">
         <v>9295000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>8792000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>9170000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>11178000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>5442000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>5024000</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2234,9 +2359,12 @@
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N54" s="3"/>
-    </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O54" s="3"/>
+    </row>
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2251,8 +2379,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2267,32 +2396,33 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>258000</v>
+      </c>
+      <c r="E57" s="3">
         <v>208000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>185000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>189000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>167000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>109000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>99000</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2302,33 +2432,36 @@
       <c r="M57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N57" s="3"/>
-    </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O57" s="3"/>
+    </row>
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1220000</v>
+      </c>
+      <c r="E58" s="3">
         <v>123000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>125000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>117000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>144000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>140000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>161000</v>
       </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2338,33 +2471,36 @@
       <c r="M58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N58" s="3"/>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O58" s="3"/>
+    </row>
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2660000</v>
+      </c>
+      <c r="E59" s="3">
         <v>1738000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>766000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>384000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>341000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>289000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>216000</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2374,33 +2510,36 @@
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N59" s="3"/>
-    </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O59" s="3"/>
+    </row>
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4627000</v>
+      </c>
+      <c r="E60" s="3">
         <v>2592000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1478000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1097000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1026000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>836000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>783000</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2410,33 +2549,36 @@
       <c r="M60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N60" s="3"/>
-    </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O60" s="3"/>
+    </row>
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>373000</v>
+      </c>
+      <c r="E61" s="3">
         <v>241000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>668000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1248000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2031000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>10878000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>8440000</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
         <v>0</v>
       </c>
@@ -2446,33 +2588,36 @@
       <c r="M61" s="3">
         <v>0</v>
       </c>
-      <c r="N61" s="3"/>
-    </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3"/>
+    </row>
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>178000</v>
+      </c>
+      <c r="E62" s="3">
         <v>74000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>147000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>137000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>84000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>6000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>9000</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2482,9 +2627,12 @@
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N62" s="3"/>
-    </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O62" s="3"/>
+    </row>
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2518,9 +2666,12 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-      <c r="N63" s="3"/>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+      <c r="O63" s="3"/>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2554,9 +2705,12 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-      <c r="N64" s="3"/>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+      <c r="O64" s="3"/>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2590,33 +2744,36 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-      <c r="N65" s="3"/>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+      <c r="O65" s="3"/>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5226000</v>
+      </c>
+      <c r="E66" s="3">
         <v>2944000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2324000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2513000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3159000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>11736000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>9248000</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2626,9 +2783,12 @@
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N66" s="3"/>
-    </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O66" s="3"/>
+    </row>
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2643,8 +2803,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2678,9 +2839,12 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-      <c r="N68" s="3"/>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+      <c r="O68" s="3"/>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2714,9 +2878,12 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-      <c r="N69" s="3"/>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+      <c r="O69" s="3"/>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2750,9 +2917,12 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-      <c r="N70" s="3"/>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3"/>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2786,33 +2956,36 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-      <c r="N71" s="3"/>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+      <c r="O71" s="3"/>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-17470000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-17347000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-16764000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-16277000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-14402000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-10490000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-7982000</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
       </c>
@@ -2822,9 +2995,12 @@
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N72" s="3"/>
-    </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O72" s="3"/>
+    </row>
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2858,9 +3034,12 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-      <c r="N73" s="3"/>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+      <c r="O73" s="3"/>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2894,9 +3073,12 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-      <c r="N74" s="3"/>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+      <c r="O74" s="3"/>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2930,33 +3112,36 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-      <c r="N75" s="3"/>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+      <c r="O75" s="3"/>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6728000</v>
+      </c>
+      <c r="E76" s="3">
         <v>6399000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>6449000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>6603000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>7733000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-6399000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-4291000</v>
       </c>
-      <c r="J76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K76" s="3" t="s">
         <v>3</v>
       </c>
@@ -2966,9 +3151,12 @@
       <c r="M76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N76" s="3"/>
-    </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O76" s="3"/>
+    </row>
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3002,38 +3190,41 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-      <c r="N77" s="3"/>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+      <c r="O77" s="3"/>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="K80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3043,33 +3234,36 @@
       <c r="M80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="N80" s="2"/>
-    </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O80" s="2"/>
+    </row>
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>268000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-105000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-434000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-1683000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-3449000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-2608000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-3747000</v>
       </c>
-      <c r="J81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3079,9 +3273,12 @@
       <c r="M81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N81" s="3"/>
-    </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O81" s="3"/>
+    </row>
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3096,32 +3293,33 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>145000</v>
+      </c>
+      <c r="E83" s="3">
         <v>122000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>128000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>129000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>109000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>126000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>109000</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3131,9 +3329,12 @@
       <c r="M83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N83" s="3"/>
-    </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O83" s="3"/>
+    </row>
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3167,9 +3368,12 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-      <c r="N84" s="3"/>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+      <c r="O84" s="3"/>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3203,9 +3407,12 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-      <c r="N85" s="3"/>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+      <c r="O85" s="3"/>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3239,9 +3446,12 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-      <c r="N86" s="3"/>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+      <c r="O86" s="3"/>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3275,9 +3485,12 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-      <c r="N87" s="3"/>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+      <c r="O87" s="3"/>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3311,33 +3524,36 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-      <c r="N88" s="3"/>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+      <c r="O88" s="3"/>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>79000</v>
+      </c>
+      <c r="E89" s="3">
         <v>852000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>86000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-798000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-954000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-643000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-2112000</v>
       </c>
-      <c r="J89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3347,9 +3563,12 @@
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N89" s="3"/>
-    </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O89" s="3"/>
+    </row>
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3364,32 +3583,33 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-97000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-77000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-71000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-58000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-73000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-22000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-98000</v>
       </c>
-      <c r="J91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K91" s="3" t="s">
         <v>3</v>
       </c>
@@ -3399,9 +3619,12 @@
       <c r="M91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N91" s="3"/>
-    </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O91" s="3"/>
+    </row>
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3435,9 +3658,12 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-      <c r="N92" s="3"/>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+      <c r="O92" s="3"/>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3471,33 +3697,36 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-      <c r="N93" s="3"/>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+      <c r="O93" s="3"/>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-782000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-231000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>1871000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1062000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2757000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-288000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>393000</v>
       </c>
-      <c r="J94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K94" s="3" t="s">
         <v>3</v>
       </c>
@@ -3507,9 +3736,12 @@
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N94" s="3"/>
-    </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O94" s="3"/>
+    </row>
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3524,8 +3756,9 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3559,9 +3792,12 @@
       <c r="M96" s="3">
         <v>0</v>
       </c>
-      <c r="N96" s="3"/>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3"/>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3595,9 +3831,12 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-      <c r="N97" s="3"/>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+      <c r="O97" s="3"/>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3631,9 +3870,12 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-      <c r="N98" s="3"/>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+      <c r="O98" s="3"/>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3667,33 +3909,36 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-      <c r="N99" s="3"/>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+      <c r="O99" s="3"/>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1095000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-771000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-770000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1122000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>6566000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1578000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1951000</v>
       </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K100" s="3" t="s">
         <v>3</v>
       </c>
@@ -3703,33 +3948,36 @@
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N100" s="3"/>
-    </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O100" s="3"/>
+    </row>
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>77000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-24000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-57000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-37000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>15000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>12000</v>
       </c>
-      <c r="J101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
@@ -3739,43 +3987,49 @@
       <c r="M101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N101" s="3"/>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O101" s="3"/>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>469000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-174000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1186000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-3039000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>2818000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>662000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>244000</v>
       </c>
-      <c r="J102" s="3">
-        <v>0</v>
-      </c>
       <c r="K102" s="3">
         <v>0</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
+      <c r="L102" s="3">
+        <v>0</v>
       </c>
       <c r="M102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N102" s="3"/>
+      <c r="N102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
